--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 11:12:30</t>
+          <t>10/15 11:13:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23602.48</t>
+          <t>23456.79</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23602.48</t>
+          <t>23456.79</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23602.48</t>
+          <t>23456.79</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/15 11:33:25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/15 11:13:31</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>190000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>23456.79</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>190000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23456.79</t>
+          <t>490000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59601.37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>23456.79</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>59601.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 11:33:25</t>
+          <t>10/15 12:50:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10/15 11:33:25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>10/15 11:13:31</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>190000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>23456.79</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>490000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>59601.37</t>
+          <t>630000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76674.54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>59601.37</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>76674.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10/15 12:52:49</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>630000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>76674.54</t>
+          <t>630000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76674.54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>76674.54</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>16674.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 12:50:36</t>
+          <t>10/15 12:53:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/15 11:33:25</t>
+          <t>10/15 12:50:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,210 +159,252 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10/15 11:33:25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>10/15 11:13:31</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>190000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>23456.79</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>10/15 12:52:49</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>630000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>76674.54</t>
+          <t>730000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>88795.75</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>16674.54</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>28795.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-2026-10-15.xlsx
@@ -328,83 +328,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>10/15 14:12:19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>28795</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>10/15 12:52:49</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>730000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>88795.75</t>
+          <t>730000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>88795.75</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>88795</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>28795.75</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.75</t>
         </is>
       </c>
     </row>
